--- a/data/merged/2026-09-23/MERGED_ES_Mite-Vacuum_2026-09-23.xlsx
+++ b/data/merged/2026-09-23/MERGED_ES_Mite-Vacuum_2026-09-23.xlsx
@@ -2926,7 +2926,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2964,7 +2964,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
@@ -3008,13 +3008,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3096,13 +3096,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3272,7 +3272,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
@@ -3322,7 +3322,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3360,13 +3360,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3404,7 +3404,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
@@ -3448,7 +3448,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
@@ -3471,50 +3471,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId29" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="30" name="Product 30">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId30" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3856,7 +3812,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR31"/>
+  <dimension ref="A1:BR30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -5649,7 +5605,7 @@
       <c r="B15" s="13"/>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>B0FBX24WH6</t>
+          <t>B0FDWVV95V</t>
         </is>
       </c>
       <c r="D15" s="14"/>
@@ -5662,23 +5618,23 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>syayw Limpiador Varuum – 68 W Fuerte Cama vacío para Limpieza ProfundasEliminador de para Mascotas vacío para Cojines de so</t>
+          <t>JIGOO T600 T600 - Tetina antiácaros/Floral Delight (aceite esencial de plantas)</t>
         </is>
       </c>
       <c r="I15" s="14"/>
       <c r="J15" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0FBX24WH6?psc=1</t>
+          <t>https://www.amazon.es/dp/B0FDWVV95V?psc=1</t>
         </is>
       </c>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61LvanTuKlL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L15" s="14" t="inlineStr">
         <is>
-          <t>B0FBX24WH6</t>
+          <t>B0FDWVV95V</t>
         </is>
       </c>
       <c r="M15" s="1"/>
@@ -5698,9 +5654,13 @@
       <c r="AA15"/>
       <c r="AB15"/>
       <c r="AC15"/>
-      <c r="AD15" s="19"/>
+      <c r="AD15" s="19">
+        <v>11</v>
+      </c>
       <c r="AE15"/>
-      <c r="AF15" s="20"/>
+      <c r="AF15" s="20">
+        <v>4.2</v>
+      </c>
       <c r="AG15" s="21">
         <v>0</v>
       </c>
@@ -5751,7 +5711,7 @@
       <c r="B16" s="13"/>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>B0FDWVV95V</t>
+          <t>B0FKRC3KQY</t>
         </is>
       </c>
       <c r="D16" s="14"/>
@@ -5764,23 +5724,23 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>JIGOO T600 T600 - Tetina antiácaros/Floral Delight (aceite esencial de plantas)</t>
+          <t>Yaasier Aspirador de Ácaros, Mini Aspirador Antiácaros para Colchones con Luz UV, Aspiradora de Mano con Filtro HEPA para Col</t>
         </is>
       </c>
       <c r="I16" s="14"/>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0FDWVV95V?psc=1</t>
+          <t>https://www.amazon.es/dp/B0FKRC3KQY?psc=1</t>
         </is>
       </c>
       <c r="K16" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/511XZVAimmL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>B0FDWVV95V</t>
+          <t>B0FKRC3KQY</t>
         </is>
       </c>
       <c r="M16" s="1"/>
@@ -5801,11 +5761,11 @@
       <c r="AB16"/>
       <c r="AC16"/>
       <c r="AD16" s="19">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AE16"/>
       <c r="AF16" s="20">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AG16" s="21">
         <v>0</v>
@@ -5857,7 +5817,7 @@
       <c r="B17" s="13"/>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>B0FKRC3KQY</t>
+          <t>B0FN3GPQZM</t>
         </is>
       </c>
       <c r="D17" s="14"/>
@@ -5870,23 +5830,23 @@
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>Yaasier Aspirador de Ácaros, Mini Aspirador Antiácaros para Colchones con Luz UV, Aspiradora de Mano con Filtro HEPA para Col</t>
+          <t>Mayking Teant Aspiradora para Colchones 2 Velocidades (14 kPa/18 kPa)</t>
         </is>
       </c>
       <c r="I17" s="14"/>
       <c r="J17" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0FKRC3KQY?psc=1</t>
+          <t>https://www.amazon.es/dp/B0FN3GPQZM?psc=1</t>
         </is>
       </c>
       <c r="K17" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/511XZVAimmL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71gt+j80L3L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L17" s="14" t="inlineStr">
         <is>
-          <t>B0FKRC3KQY</t>
+          <t>B0FN3GPQZM</t>
         </is>
       </c>
       <c r="M17" s="1"/>
@@ -5907,11 +5867,11 @@
       <c r="AB17"/>
       <c r="AC17"/>
       <c r="AD17" s="19">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AE17"/>
       <c r="AF17" s="20">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="AG17" s="21">
         <v>0</v>
@@ -5963,7 +5923,7 @@
       <c r="B18" s="13"/>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>B0FN3GPQZM</t>
+          <t>B0FPQMRBYZ</t>
         </is>
       </c>
       <c r="D18" s="14"/>
@@ -5976,23 +5936,23 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>Mayking Teant Aspiradora para Colchones 2 Velocidades (14 kPa/18 kPa)</t>
+          <t>KÄRCHER Limpiador de colchones VCH 4 UVClean, 500 W, Peso: 2,1 kgsLimpieza profunda e higiénica con luz UV-C, rodillo percu</t>
         </is>
       </c>
       <c r="I18" s="14"/>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0FN3GPQZM?psc=1</t>
+          <t>https://www.amazon.es/dp/B0FPQMRBYZ?psc=1</t>
         </is>
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71gt+j80L3L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/81RtcozDdwL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>B0FN3GPQZM</t>
+          <t>B0FPQMRBYZ</t>
         </is>
       </c>
       <c r="M18" s="1"/>
@@ -6008,12 +5968,14 @@
       <c r="W18" s="15"/>
       <c r="X18" s="15"/>
       <c r="Y18"/>
-      <c r="Z18" s="4"/>
+      <c r="Z18" s="4">
+        <v>85.63</v>
+      </c>
       <c r="AA18"/>
       <c r="AB18"/>
       <c r="AC18"/>
       <c r="AD18" s="19">
-        <v>40</v>
+        <v>193</v>
       </c>
       <c r="AE18"/>
       <c r="AF18" s="20">
@@ -6069,7 +6031,7 @@
       <c r="B19" s="13"/>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>B0FPQMRBYZ</t>
+          <t>B0FVS559GZ</t>
         </is>
       </c>
       <c r="D19" s="14"/>
@@ -6082,23 +6044,23 @@
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>KÄRCHER Limpiador de colchones VCH 4 UVClean, 500 W, Peso: 2,1 kgsLimpieza profunda e higiénica con luz UV-C, rodillo percu</t>
+          <t>Yaasier Aspirador de ácaros con luz UV, Mini aspiradora con Filtro HEPA, Aspirador antiacaros con depósito de Polvo Permanent</t>
         </is>
       </c>
       <c r="I19" s="14"/>
       <c r="J19" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0FPQMRBYZ?psc=1</t>
+          <t>https://www.amazon.es/dp/B0FVS559GZ?psc=1</t>
         </is>
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/81RtcozDdwL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L19" s="14" t="inlineStr">
         <is>
-          <t>B0FPQMRBYZ</t>
+          <t>B0FVS559GZ</t>
         </is>
       </c>
       <c r="M19" s="1"/>
@@ -6114,18 +6076,16 @@
       <c r="W19" s="15"/>
       <c r="X19" s="15"/>
       <c r="Y19"/>
-      <c r="Z19" s="4">
-        <v>85.63</v>
-      </c>
+      <c r="Z19" s="4"/>
       <c r="AA19"/>
       <c r="AB19"/>
       <c r="AC19"/>
       <c r="AD19" s="19">
-        <v>193</v>
+        <v>28</v>
       </c>
       <c r="AE19"/>
       <c r="AF19" s="20">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="AG19" s="21">
         <v>0</v>
@@ -6177,7 +6137,7 @@
       <c r="B20" s="13"/>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>B0FVS559GZ</t>
+          <t>B0FYM1D13D</t>
         </is>
       </c>
       <c r="D20" s="14"/>
@@ -6190,13 +6150,13 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>Yaasier Aspirador de ácaros con luz UV, Mini aspiradora con Filtro HEPA, Aspirador antiacaros con depósito de Polvo Permanent</t>
+          <t>Aspirador de ácaros con luz UV, Mini aspiradora con Filtro HEPA, Aspirador antiacaros con depósito de Polvo Permanente para c</t>
         </is>
       </c>
       <c r="I20" s="14"/>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0FVS559GZ?psc=1</t>
+          <t>https://www.amazon.es/dp/B0FYM1D13D?psc=1</t>
         </is>
       </c>
       <c r="K20" s="14" t="inlineStr">
@@ -6206,7 +6166,7 @@
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>B0FVS559GZ</t>
+          <t>B0FYM1D13D</t>
         </is>
       </c>
       <c r="M20" s="1"/>
@@ -6227,11 +6187,11 @@
       <c r="AB20"/>
       <c r="AC20"/>
       <c r="AD20" s="19">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="AE20"/>
       <c r="AF20" s="20">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AG20" s="21">
         <v>0</v>
@@ -6283,7 +6243,7 @@
       <c r="B21" s="13"/>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>B0FYM1D13D</t>
+          <t>B0G4RSJQVT</t>
         </is>
       </c>
       <c r="D21" s="14"/>
@@ -6296,23 +6256,23 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>Aspirador de ácaros con luz UV, Mini aspiradora con Filtro HEPA, Aspirador antiacaros con depósito de Polvo Permanente para c</t>
+          <t>Lubluelu Aspirador de ácaros 3 en 1 para colchones, 18 KPa fuerte potencia de succión, limpiador de colchones contra ácaros,</t>
         </is>
       </c>
       <c r="I21" s="14"/>
       <c r="J21" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0FYM1D13D?psc=1</t>
+          <t>https://www.amazon.es/dp/B0G4RSJQVT?psc=1</t>
         </is>
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71mJa10XC6L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L21" s="14" t="inlineStr">
         <is>
-          <t>B0FYM1D13D</t>
+          <t>B0G4RSJQVT</t>
         </is>
       </c>
       <c r="M21" s="1"/>
@@ -6333,11 +6293,11 @@
       <c r="AB21"/>
       <c r="AC21"/>
       <c r="AD21" s="19">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="AE21"/>
       <c r="AF21" s="20">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="AG21" s="21">
         <v>0</v>
@@ -6389,7 +6349,7 @@
       <c r="B22" s="13"/>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>B0G4RSJQVT</t>
+          <t>B0GF7CNTYL</t>
         </is>
       </c>
       <c r="D22" s="14"/>
@@ -6402,23 +6362,23 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Lubluelu Aspirador de ácaros 3 en 1 para colchones, 18 KPa fuerte potencia de succión, limpiador de colchones contra ácaros,</t>
+          <t>Aspirador de colchón UV-C y ultrasónico doble vaso para cama y sofásAspirador de ácaros inalámbrico para colchones, sofás d</t>
         </is>
       </c>
       <c r="I22" s="14"/>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0G4RSJQVT?psc=1</t>
+          <t>https://www.amazon.es/dp/B0GF7CNTYL?psc=1</t>
         </is>
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71mJa10XC6L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71H9bRmoUnL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>B0G4RSJQVT</t>
+          <t>B0GF7CNTYL</t>
         </is>
       </c>
       <c r="M22" s="1"/>
@@ -6438,13 +6398,9 @@
       <c r="AA22"/>
       <c r="AB22"/>
       <c r="AC22"/>
-      <c r="AD22" s="19">
-        <v>26</v>
-      </c>
+      <c r="AD22" s="19"/>
       <c r="AE22"/>
-      <c r="AF22" s="20">
-        <v>4.6</v>
-      </c>
+      <c r="AF22" s="20"/>
       <c r="AG22" s="21">
         <v>0</v>
       </c>
@@ -6495,7 +6451,7 @@
       <c r="B23" s="13"/>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>B0GF7CNTYL</t>
+          <t>B0GFCJ4JWY</t>
         </is>
       </c>
       <c r="D23" s="14"/>
@@ -6508,23 +6464,23 @@
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>Aspirador de colchón UV-C y ultrasónico doble vaso para cama y sofásAspirador de ácaros inalámbrico para colchones, sofás d</t>
+          <t>PEXCHO Aspirador de ácaros PM600 con luz UV, 500 W, para alérgicos, Elimina el 99,9% de los ácaros del Polvo, alérgenos, Pelo</t>
         </is>
       </c>
       <c r="I23" s="14"/>
       <c r="J23" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0GF7CNTYL?psc=1</t>
+          <t>https://www.amazon.es/dp/B0GFCJ4JWY?psc=1</t>
         </is>
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71H9bRmoUnL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71AmFHqQF6L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>B0GF7CNTYL</t>
+          <t>B0GFCJ4JWY</t>
         </is>
       </c>
       <c r="M23" s="1"/>
@@ -6544,9 +6500,13 @@
       <c r="AA23"/>
       <c r="AB23"/>
       <c r="AC23"/>
-      <c r="AD23" s="19"/>
+      <c r="AD23" s="19">
+        <v>775</v>
+      </c>
       <c r="AE23"/>
-      <c r="AF23" s="20"/>
+      <c r="AF23" s="20">
+        <v>4.6</v>
+      </c>
       <c r="AG23" s="21">
         <v>0</v>
       </c>
@@ -6597,7 +6557,7 @@
       <c r="B24" s="13"/>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>B0GFCJ4JWY</t>
+          <t>B0GHQLQBYD</t>
         </is>
       </c>
       <c r="D24" s="14"/>
@@ -6610,23 +6570,23 @@
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>PEXCHO Aspirador de ácaros PM600 con luz UV, 500 W, para alérgicos, Elimina el 99,9% de los ácaros del Polvo, alérgenos, Pelo</t>
+          <t>Aspiradora Antiacaros, Aspirador Acaros Sofa y Colchon con Una Gran Potencia de Aspiración, Aspirador Antiacaros para Colchon</t>
         </is>
       </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0GFCJ4JWY?psc=1</t>
+          <t>https://www.amazon.es/dp/B0GHQLQBYD?psc=1</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71AmFHqQF6L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/610gU-iwIJL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>B0GFCJ4JWY</t>
+          <t>B0GHQLQBYD</t>
         </is>
       </c>
       <c r="M24" s="1"/>
@@ -6647,11 +6607,11 @@
       <c r="AB24"/>
       <c r="AC24"/>
       <c r="AD24" s="19">
-        <v>775</v>
+        <v>21</v>
       </c>
       <c r="AE24"/>
       <c r="AF24" s="20">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="AG24" s="21">
         <v>0</v>
@@ -6703,7 +6663,7 @@
       <c r="B25" s="13"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>B0GHQLQBYD</t>
+          <t>B0GMPWRDGV</t>
         </is>
       </c>
       <c r="D25" s="14"/>
@@ -6716,23 +6676,23 @@
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>Aspiradora Antiacaros, Aspirador Acaros Sofa y Colchon con Una Gran Potencia de Aspiración, Aspirador Antiacaros para Colchon</t>
+          <t>Elecbee Aspirador de ácaros inalámbrico para colchón, Aspirador de ácaros con luz UV, Pantalla LED, aspiradora de colchón ult</t>
         </is>
       </c>
       <c r="I25" s="14"/>
       <c r="J25" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0GHQLQBYD?psc=1</t>
+          <t>https://www.amazon.es/dp/B0GMPWRDGV?psc=1</t>
         </is>
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/610gU-iwIJL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/811Brxwo2jL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>B0GHQLQBYD</t>
+          <t>B0GMPWRDGV</t>
         </is>
       </c>
       <c r="M25" s="1"/>
@@ -6753,11 +6713,11 @@
       <c r="AB25"/>
       <c r="AC25"/>
       <c r="AD25" s="19">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE25"/>
       <c r="AF25" s="20">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="AG25" s="21">
         <v>0</v>
@@ -6809,7 +6769,7 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>B0GMPWRDGV</t>
+          <t>B0GXVR9CY9</t>
         </is>
       </c>
       <c r="D26" s="14"/>
@@ -6822,23 +6782,23 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>Elecbee Aspirador de ácaros inalámbrico para colchón, Aspirador de ácaros con luz UV, Pantalla LED, aspiradora de colchón ult</t>
+          <t>Jimmy BX8 Aspirador de Mano para Colchones, 600W 15kPa Succion Aspiradora Antiacaros con Ultravioleta UV-C, Secado Termico 65</t>
         </is>
       </c>
       <c r="I26" s="14"/>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0GMPWRDGV?psc=1</t>
+          <t>https://www.amazon.es/dp/B0GXVR9CY9?psc=1</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/811Brxwo2jL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71um1FaVwRL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>B0GMPWRDGV</t>
+          <t>B0GXVR9CY9</t>
         </is>
       </c>
       <c r="M26" s="1"/>
@@ -6859,11 +6819,11 @@
       <c r="AB26"/>
       <c r="AC26"/>
       <c r="AD26" s="19">
-        <v>22</v>
+        <v>183</v>
       </c>
       <c r="AE26"/>
       <c r="AF26" s="20">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AG26" s="21">
         <v>0</v>
@@ -6915,7 +6875,7 @@
       <c r="B27" s="13"/>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>B0GXVR9CY9</t>
+          <t>B0GYS43G8G</t>
         </is>
       </c>
       <c r="D27" s="14"/>
@@ -6928,23 +6888,23 @@
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>Jimmy BX8 Aspirador de Mano para Colchones, 600W 15kPa Succion Aspiradora Antiacaros con Ultravioleta UV-C, Secado Termico 65</t>
+          <t>Aspiradora De Acaros, Aspiradora Antiacaros con Triple Filtración Y Filtro Lavable, Vibración De Alta Frecuencia, Maquina Ant</t>
         </is>
       </c>
       <c r="I27" s="14"/>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0GXVR9CY9?psc=1</t>
+          <t>https://www.amazon.es/dp/B0GYS43G8G?psc=1</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71um1FaVwRL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51JXrvAAoZL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>B0GXVR9CY9</t>
+          <t>B0GYS43G8G</t>
         </is>
       </c>
       <c r="M27" s="1"/>
@@ -6965,11 +6925,11 @@
       <c r="AB27"/>
       <c r="AC27"/>
       <c r="AD27" s="19">
-        <v>183</v>
+        <v>2</v>
       </c>
       <c r="AE27"/>
       <c r="AF27" s="20">
-        <v>4.6</v>
+        <v>1</v>
       </c>
       <c r="AG27" s="21">
         <v>0</v>
@@ -7021,7 +6981,7 @@
       <c r="B28" s="13"/>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>B0GYS43G8G</t>
+          <t>B0H8Z6R4ZK</t>
         </is>
       </c>
       <c r="D28" s="14"/>
@@ -7034,23 +6994,23 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Aspiradora De Acaros, Aspiradora Antiacaros con Triple Filtración Y Filtro Lavable, Vibración De Alta Frecuencia, Maquina Ant</t>
+          <t>Aspirador de colchón recargable inalámbrico portátil para camas sofássAspirador de mano silencioso, limpiador profundo inte</t>
         </is>
       </c>
       <c r="I28" s="14"/>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0GYS43G8G?psc=1</t>
+          <t>https://www.amazon.es/dp/B0H8Z6R4ZK?psc=1</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51JXrvAAoZL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61HKr6BnAHL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>B0GYS43G8G</t>
+          <t>B0H8Z6R4ZK</t>
         </is>
       </c>
       <c r="M28" s="1"/>
@@ -7070,13 +7030,9 @@
       <c r="AA28"/>
       <c r="AB28"/>
       <c r="AC28"/>
-      <c r="AD28" s="19">
-        <v>2</v>
-      </c>
+      <c r="AD28" s="19"/>
       <c r="AE28"/>
-      <c r="AF28" s="20">
-        <v>1</v>
-      </c>
+      <c r="AF28" s="20"/>
       <c r="AG28" s="21">
         <v>0</v>
       </c>
@@ -7127,7 +7083,7 @@
       <c r="B29" s="13"/>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>B0H8Z6R4ZK</t>
+          <t>B0HFN6BP5R</t>
         </is>
       </c>
       <c r="D29" s="14"/>
@@ -7140,23 +7096,23 @@
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>Aspirador de colchón recargable inalámbrico portátil para camas sofássAspirador de mano silencioso, limpiador profundo inte</t>
+          <t>Lubluelu Aspirador Antiácaros Inalámbrico 20 kPa para Colchones UV-CsAspirador de Colchones con Limpieza Profunda, hasta 99</t>
         </is>
       </c>
       <c r="I29" s="14"/>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0H8Z6R4ZK?psc=1</t>
+          <t>https://www.amazon.es/dp/B0HFN6BP5R?psc=1</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61HKr6BnAHL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/6174GoAaLTL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>B0H8Z6R4ZK</t>
+          <t>B0HFN6BP5R</t>
         </is>
       </c>
       <c r="M29" s="1"/>
@@ -7176,9 +7132,13 @@
       <c r="AA29"/>
       <c r="AB29"/>
       <c r="AC29"/>
-      <c r="AD29" s="19"/>
+      <c r="AD29" s="19">
+        <v>29</v>
+      </c>
       <c r="AE29"/>
-      <c r="AF29" s="20"/>
+      <c r="AF29" s="20">
+        <v>4.7</v>
+      </c>
       <c r="AG29" s="21">
         <v>0</v>
       </c>
@@ -7229,7 +7189,7 @@
       <c r="B30" s="13"/>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>B0HFN6BP5R</t>
+          <t>B0HG11J16S</t>
         </is>
       </c>
       <c r="D30" s="14"/>
@@ -7242,23 +7202,23 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Lubluelu Aspirador Antiácaros Inalámbrico 20 kPa para Colchones UV-CsAspirador de Colchones con Limpieza Profunda, hasta 99</t>
+          <t>Beghdhu Aspiradora Antiacaros para Colchones sin Cable</t>
         </is>
       </c>
       <c r="I30" s="14"/>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0HFN6BP5R?psc=1</t>
+          <t>https://www.amazon.es/dp/B0HG11J16S?psc=1</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/6174GoAaLTL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71pvlE5JbtL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>B0HFN6BP5R</t>
+          <t>B0HG11J16S</t>
         </is>
       </c>
       <c r="M30" s="1"/>
@@ -7279,11 +7239,11 @@
       <c r="AB30"/>
       <c r="AC30"/>
       <c r="AD30" s="19">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="AE30"/>
       <c r="AF30" s="20">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="AG30" s="21">
         <v>0</v>
@@ -7327,112 +7287,6 @@
       <c r="BP30"/>
       <c r="BQ30" s="22"/>
       <c r="BR30"/>
-    </row>
-    <row r="31" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="13">
-        <v>30</v>
-      </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="14" t="inlineStr">
-        <is>
-          <t>B0HG11J16S</t>
-        </is>
-      </c>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31"/>
-      <c r="G31" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.esundefined</t>
-        </is>
-      </c>
-      <c r="H31" s="14" t="inlineStr">
-        <is>
-          <t>Beghdhu Aspiradora Antiacaros para Colchones sin Cable</t>
-        </is>
-      </c>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/dp/B0HG11J16S?psc=1</t>
-        </is>
-      </c>
-      <c r="K31" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71pvlE5JbtL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L31" s="14" t="inlineStr">
-        <is>
-          <t>B0HG11J16S</t>
-        </is>
-      </c>
-      <c r="M31" s="1"/>
-      <c r="N31" s="14"/>
-      <c r="O31" s="15"/>
-      <c r="P31" s="15"/>
-      <c r="Q31" s="16"/>
-      <c r="R31" s="17"/>
-      <c r="S31" s="18"/>
-      <c r="T31" s="15"/>
-      <c r="U31" s="16"/>
-      <c r="V31" s="15"/>
-      <c r="W31" s="15"/>
-      <c r="X31" s="15"/>
-      <c r="Y31"/>
-      <c r="Z31" s="4"/>
-      <c r="AA31"/>
-      <c r="AB31"/>
-      <c r="AC31"/>
-      <c r="AD31" s="19">
-        <v>3</v>
-      </c>
-      <c r="AE31"/>
-      <c r="AF31" s="20">
-        <v>2.6</v>
-      </c>
-      <c r="AG31" s="21">
-        <v>0</v>
-      </c>
-      <c r="AH31"/>
-      <c r="AI31" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ31"/>
-      <c r="AK31" s="1"/>
-      <c r="AL31" s="19"/>
-      <c r="AM31"/>
-      <c r="AN31" s="13"/>
-      <c r="AO31" s="13"/>
-      <c r="AP31"/>
-      <c r="AQ31" s="19"/>
-      <c r="AR31"/>
-      <c r="AS31"/>
-      <c r="AT31"/>
-      <c r="AU31" s="13"/>
-      <c r="AV31" s="14"/>
-      <c r="AW31" s="13"/>
-      <c r="AX31" s="13"/>
-      <c r="AY31" s="13"/>
-      <c r="AZ31" s="13"/>
-      <c r="BA31" s="13"/>
-      <c r="BB31" s="13"/>
-      <c r="BC31" s="13"/>
-      <c r="BD31" s="13"/>
-      <c r="BE31" s="13"/>
-      <c r="BF31" s="13"/>
-      <c r="BG31" s="13"/>
-      <c r="BH31" s="14"/>
-      <c r="BI31"/>
-      <c r="BJ31"/>
-      <c r="BK31" s="22"/>
-      <c r="BL31"/>
-      <c r="BM31" s="22"/>
-      <c r="BN31"/>
-      <c r="BO31" s="22"/>
-      <c r="BP31"/>
-      <c r="BQ31" s="22"/>
-      <c r="BR31"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7503,93 +7357,88 @@
     <hyperlink ref="J14" r:id="rId63" tooltip="https://www.amazon.es/dp/B0FBGQY9YP?psc=1"/>
     <hyperlink ref="K14" r:id="rId64" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71OWNtREIXL._AC_UL300_SR300,200_.jpg"/>
     <hyperlink ref="L14" r:id="rId65" tooltip="https://www.amazon.es/dp/B0FBGQY9YP"/>
-    <hyperlink ref="C15" r:id="rId66" tooltip="https://www.amazon.es/dp/B0FBX24WH6"/>
+    <hyperlink ref="C15" r:id="rId66" tooltip="https://www.amazon.es/dp/B0FDWVV95V"/>
     <hyperlink ref="G15" r:id="rId67" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J15" r:id="rId68" tooltip="https://www.amazon.es/dp/B0FBX24WH6?psc=1"/>
-    <hyperlink ref="K15" r:id="rId69" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61LvanTuKlL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L15" r:id="rId70" tooltip="https://www.amazon.es/dp/B0FBX24WH6"/>
-    <hyperlink ref="C16" r:id="rId71" tooltip="https://www.amazon.es/dp/B0FDWVV95V"/>
+    <hyperlink ref="J15" r:id="rId68" tooltip="https://www.amazon.es/dp/B0FDWVV95V?psc=1"/>
+    <hyperlink ref="K15" r:id="rId69" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L15" r:id="rId70" tooltip="https://www.amazon.es/dp/B0FDWVV95V"/>
+    <hyperlink ref="C16" r:id="rId71" tooltip="https://www.amazon.es/dp/B0FKRC3KQY"/>
     <hyperlink ref="G16" r:id="rId72" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J16" r:id="rId73" tooltip="https://www.amazon.es/dp/B0FDWVV95V?psc=1"/>
-    <hyperlink ref="K16" r:id="rId74" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L16" r:id="rId75" tooltip="https://www.amazon.es/dp/B0FDWVV95V"/>
-    <hyperlink ref="C17" r:id="rId76" tooltip="https://www.amazon.es/dp/B0FKRC3KQY"/>
+    <hyperlink ref="J16" r:id="rId73" tooltip="https://www.amazon.es/dp/B0FKRC3KQY?psc=1"/>
+    <hyperlink ref="K16" r:id="rId74" tooltip="https://images-eu.ssl-images-amazon.com/images/I/511XZVAimmL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L16" r:id="rId75" tooltip="https://www.amazon.es/dp/B0FKRC3KQY"/>
+    <hyperlink ref="C17" r:id="rId76" tooltip="https://www.amazon.es/dp/B0FN3GPQZM"/>
     <hyperlink ref="G17" r:id="rId77" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J17" r:id="rId78" tooltip="https://www.amazon.es/dp/B0FKRC3KQY?psc=1"/>
-    <hyperlink ref="K17" r:id="rId79" tooltip="https://images-eu.ssl-images-amazon.com/images/I/511XZVAimmL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L17" r:id="rId80" tooltip="https://www.amazon.es/dp/B0FKRC3KQY"/>
-    <hyperlink ref="C18" r:id="rId81" tooltip="https://www.amazon.es/dp/B0FN3GPQZM"/>
+    <hyperlink ref="J17" r:id="rId78" tooltip="https://www.amazon.es/dp/B0FN3GPQZM?psc=1"/>
+    <hyperlink ref="K17" r:id="rId79" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71gt+j80L3L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L17" r:id="rId80" tooltip="https://www.amazon.es/dp/B0FN3GPQZM"/>
+    <hyperlink ref="C18" r:id="rId81" tooltip="https://www.amazon.es/dp/B0FPQMRBYZ"/>
     <hyperlink ref="G18" r:id="rId82" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J18" r:id="rId83" tooltip="https://www.amazon.es/dp/B0FN3GPQZM?psc=1"/>
-    <hyperlink ref="K18" r:id="rId84" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71gt+j80L3L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L18" r:id="rId85" tooltip="https://www.amazon.es/dp/B0FN3GPQZM"/>
-    <hyperlink ref="C19" r:id="rId86" tooltip="https://www.amazon.es/dp/B0FPQMRBYZ"/>
+    <hyperlink ref="J18" r:id="rId83" tooltip="https://www.amazon.es/dp/B0FPQMRBYZ?psc=1"/>
+    <hyperlink ref="K18" r:id="rId84" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81RtcozDdwL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L18" r:id="rId85" tooltip="https://www.amazon.es/dp/B0FPQMRBYZ"/>
+    <hyperlink ref="C19" r:id="rId86" tooltip="https://www.amazon.es/dp/B0FVS559GZ"/>
     <hyperlink ref="G19" r:id="rId87" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J19" r:id="rId88" tooltip="https://www.amazon.es/dp/B0FPQMRBYZ?psc=1"/>
-    <hyperlink ref="K19" r:id="rId89" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81RtcozDdwL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L19" r:id="rId90" tooltip="https://www.amazon.es/dp/B0FPQMRBYZ"/>
-    <hyperlink ref="C20" r:id="rId91" tooltip="https://www.amazon.es/dp/B0FVS559GZ"/>
+    <hyperlink ref="J19" r:id="rId88" tooltip="https://www.amazon.es/dp/B0FVS559GZ?psc=1"/>
+    <hyperlink ref="K19" r:id="rId89" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L19" r:id="rId90" tooltip="https://www.amazon.es/dp/B0FVS559GZ"/>
+    <hyperlink ref="C20" r:id="rId91" tooltip="https://www.amazon.es/dp/B0FYM1D13D"/>
     <hyperlink ref="G20" r:id="rId92" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J20" r:id="rId93" tooltip="https://www.amazon.es/dp/B0FVS559GZ?psc=1"/>
+    <hyperlink ref="J20" r:id="rId93" tooltip="https://www.amazon.es/dp/B0FYM1D13D?psc=1"/>
     <hyperlink ref="K20" r:id="rId94" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L20" r:id="rId95" tooltip="https://www.amazon.es/dp/B0FVS559GZ"/>
-    <hyperlink ref="C21" r:id="rId96" tooltip="https://www.amazon.es/dp/B0FYM1D13D"/>
+    <hyperlink ref="L20" r:id="rId95" tooltip="https://www.amazon.es/dp/B0FYM1D13D"/>
+    <hyperlink ref="C21" r:id="rId96" tooltip="https://www.amazon.es/dp/B0G4RSJQVT"/>
     <hyperlink ref="G21" r:id="rId97" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J21" r:id="rId98" tooltip="https://www.amazon.es/dp/B0FYM1D13D?psc=1"/>
-    <hyperlink ref="K21" r:id="rId99" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L21" r:id="rId100" tooltip="https://www.amazon.es/dp/B0FYM1D13D"/>
-    <hyperlink ref="C22" r:id="rId101" tooltip="https://www.amazon.es/dp/B0G4RSJQVT"/>
+    <hyperlink ref="J21" r:id="rId98" tooltip="https://www.amazon.es/dp/B0G4RSJQVT?psc=1"/>
+    <hyperlink ref="K21" r:id="rId99" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71mJa10XC6L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L21" r:id="rId100" tooltip="https://www.amazon.es/dp/B0G4RSJQVT"/>
+    <hyperlink ref="C22" r:id="rId101" tooltip="https://www.amazon.es/dp/B0GF7CNTYL"/>
     <hyperlink ref="G22" r:id="rId102" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J22" r:id="rId103" tooltip="https://www.amazon.es/dp/B0G4RSJQVT?psc=1"/>
-    <hyperlink ref="K22" r:id="rId104" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71mJa10XC6L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L22" r:id="rId105" tooltip="https://www.amazon.es/dp/B0G4RSJQVT"/>
-    <hyperlink ref="C23" r:id="rId106" tooltip="https://www.amazon.es/dp/B0GF7CNTYL"/>
+    <hyperlink ref="J22" r:id="rId103" tooltip="https://www.amazon.es/dp/B0GF7CNTYL?psc=1"/>
+    <hyperlink ref="K22" r:id="rId104" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71H9bRmoUnL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L22" r:id="rId105" tooltip="https://www.amazon.es/dp/B0GF7CNTYL"/>
+    <hyperlink ref="C23" r:id="rId106" tooltip="https://www.amazon.es/dp/B0GFCJ4JWY"/>
     <hyperlink ref="G23" r:id="rId107" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J23" r:id="rId108" tooltip="https://www.amazon.es/dp/B0GF7CNTYL?psc=1"/>
-    <hyperlink ref="K23" r:id="rId109" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71H9bRmoUnL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L23" r:id="rId110" tooltip="https://www.amazon.es/dp/B0GF7CNTYL"/>
-    <hyperlink ref="C24" r:id="rId111" tooltip="https://www.amazon.es/dp/B0GFCJ4JWY"/>
+    <hyperlink ref="J23" r:id="rId108" tooltip="https://www.amazon.es/dp/B0GFCJ4JWY?psc=1"/>
+    <hyperlink ref="K23" r:id="rId109" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71AmFHqQF6L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L23" r:id="rId110" tooltip="https://www.amazon.es/dp/B0GFCJ4JWY"/>
+    <hyperlink ref="C24" r:id="rId111" tooltip="https://www.amazon.es/dp/B0GHQLQBYD"/>
     <hyperlink ref="G24" r:id="rId112" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J24" r:id="rId113" tooltip="https://www.amazon.es/dp/B0GFCJ4JWY?psc=1"/>
-    <hyperlink ref="K24" r:id="rId114" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71AmFHqQF6L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L24" r:id="rId115" tooltip="https://www.amazon.es/dp/B0GFCJ4JWY"/>
-    <hyperlink ref="C25" r:id="rId116" tooltip="https://www.amazon.es/dp/B0GHQLQBYD"/>
+    <hyperlink ref="J24" r:id="rId113" tooltip="https://www.amazon.es/dp/B0GHQLQBYD?psc=1"/>
+    <hyperlink ref="K24" r:id="rId114" tooltip="https://images-eu.ssl-images-amazon.com/images/I/610gU-iwIJL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L24" r:id="rId115" tooltip="https://www.amazon.es/dp/B0GHQLQBYD"/>
+    <hyperlink ref="C25" r:id="rId116" tooltip="https://www.amazon.es/dp/B0GMPWRDGV"/>
     <hyperlink ref="G25" r:id="rId117" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J25" r:id="rId118" tooltip="https://www.amazon.es/dp/B0GHQLQBYD?psc=1"/>
-    <hyperlink ref="K25" r:id="rId119" tooltip="https://images-eu.ssl-images-amazon.com/images/I/610gU-iwIJL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L25" r:id="rId120" tooltip="https://www.amazon.es/dp/B0GHQLQBYD"/>
-    <hyperlink ref="C26" r:id="rId121" tooltip="https://www.amazon.es/dp/B0GMPWRDGV"/>
+    <hyperlink ref="J25" r:id="rId118" tooltip="https://www.amazon.es/dp/B0GMPWRDGV?psc=1"/>
+    <hyperlink ref="K25" r:id="rId119" tooltip="https://images-eu.ssl-images-amazon.com/images/I/811Brxwo2jL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L25" r:id="rId120" tooltip="https://www.amazon.es/dp/B0GMPWRDGV"/>
+    <hyperlink ref="C26" r:id="rId121" tooltip="https://www.amazon.es/dp/B0GXVR9CY9"/>
     <hyperlink ref="G26" r:id="rId122" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J26" r:id="rId123" tooltip="https://www.amazon.es/dp/B0GMPWRDGV?psc=1"/>
-    <hyperlink ref="K26" r:id="rId124" tooltip="https://images-eu.ssl-images-amazon.com/images/I/811Brxwo2jL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L26" r:id="rId125" tooltip="https://www.amazon.es/dp/B0GMPWRDGV"/>
-    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.es/dp/B0GXVR9CY9"/>
+    <hyperlink ref="J26" r:id="rId123" tooltip="https://www.amazon.es/dp/B0GXVR9CY9?psc=1"/>
+    <hyperlink ref="K26" r:id="rId124" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71um1FaVwRL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L26" r:id="rId125" tooltip="https://www.amazon.es/dp/B0GXVR9CY9"/>
+    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.es/dp/B0GYS43G8G"/>
     <hyperlink ref="G27" r:id="rId127" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.es/dp/B0GXVR9CY9?psc=1"/>
-    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71um1FaVwRL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.es/dp/B0GXVR9CY9"/>
-    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.es/dp/B0GYS43G8G"/>
+    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.es/dp/B0GYS43G8G?psc=1"/>
+    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51JXrvAAoZL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.es/dp/B0GYS43G8G"/>
+    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.es/dp/B0H8Z6R4ZK"/>
     <hyperlink ref="G28" r:id="rId132" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.es/dp/B0GYS43G8G?psc=1"/>
-    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51JXrvAAoZL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.es/dp/B0GYS43G8G"/>
-    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.es/dp/B0H8Z6R4ZK"/>
+    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.es/dp/B0H8Z6R4ZK?psc=1"/>
+    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61HKr6BnAHL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.es/dp/B0H8Z6R4ZK"/>
+    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.es/dp/B0HFN6BP5R"/>
     <hyperlink ref="G29" r:id="rId137" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.es/dp/B0H8Z6R4ZK?psc=1"/>
-    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61HKr6BnAHL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.es/dp/B0H8Z6R4ZK"/>
-    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.es/dp/B0HFN6BP5R"/>
+    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.es/dp/B0HFN6BP5R?psc=1"/>
+    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-eu.ssl-images-amazon.com/images/I/6174GoAaLTL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.es/dp/B0HFN6BP5R"/>
+    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.es/dp/B0HG11J16S"/>
     <hyperlink ref="G30" r:id="rId142" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.es/dp/B0HFN6BP5R?psc=1"/>
-    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-eu.ssl-images-amazon.com/images/I/6174GoAaLTL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.es/dp/B0HFN6BP5R"/>
-    <hyperlink ref="C31" r:id="rId146" tooltip="https://www.amazon.es/dp/B0HG11J16S"/>
-    <hyperlink ref="G31" r:id="rId147" tooltip="https://www.amazon.esundefined"/>
-    <hyperlink ref="J31" r:id="rId148" tooltip="https://www.amazon.es/dp/B0HG11J16S?psc=1"/>
-    <hyperlink ref="K31" r:id="rId149" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71pvlE5JbtL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L31" r:id="rId150" tooltip="https://www.amazon.es/dp/B0HG11J16S"/>
+    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.es/dp/B0HG11J16S?psc=1"/>
+    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71pvlE5JbtL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.es/dp/B0HG11J16S"/>
   </hyperlinks>
-  <drawing r:id="rId151"/>
+  <drawing r:id="rId146"/>
 </worksheet>
 </file>
 
